--- a/FREVS/westwood plaza.xlsx
+++ b/FREVS/westwood plaza.xlsx
@@ -938,9 +938,9 @@
           <t>Ownership</t>
         </is>
       </c>
-      <c r="B101" s="18">
+      <c r="B101" t="n" s="18">
         <f>B5</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -949,9 +949,9 @@
           <t>Book carrying value</t>
         </is>
       </c>
-      <c r="B102" s="19">
+      <c r="B102" t="n" s="19">
         <f>B21</f>
-        <v/>
+        <v>7217000</v>
       </c>
     </row>
     <row r="103">
@@ -960,9 +960,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B103" s="19">
+      <c r="B103" t="n" s="19">
         <f>B27</f>
-        <v/>
+        <v>28800000</v>
       </c>
     </row>
     <row r="104">
@@ -971,9 +971,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="B104" s="19">
+      <c r="B104" t="n" s="19">
         <f>B28</f>
-        <v/>
+        <v>28800000</v>
       </c>
     </row>
     <row r="105">
@@ -992,9 +992,9 @@
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B106" s="19">
+      <c r="B106" t="n" s="19">
         <f>B22</f>
-        <v/>
+        <v>9459000</v>
       </c>
     </row>
     <row r="107">
